--- a/Exc2/FURPS_table.xlsx
+++ b/Exc2/FURPS_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\architecture-sprint-9\Exc2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1372DE31-A1CE-4B38-B400-5647045C0C3C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F8BEB5-5CFC-4354-B032-5B84E11633B7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="21600" windowHeight="14235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
   <si>
     <t>Код</t>
   </si>
@@ -74,12 +74,6 @@
   </si>
   <si>
     <t>HTTPS сайт</t>
-  </si>
-  <si>
-    <t>Реализовать в АБС весь текущий процесс согласования ставки по заявке</t>
-  </si>
-  <si>
-    <t>В интернет-банке клиент видит список доступных депозитов с актуальными ставками и персонализированные ставки лично для него</t>
   </si>
   <si>
     <t>При доработках во всех системах нужно как можно больше использовать технологии, которые уже есть в банке</t>
@@ -120,9 +114,6 @@
 Сайт — собственная разработка банка на PHP и React.js</t>
   </si>
   <si>
-    <t>Только в рамках MVP депозитного направления</t>
-  </si>
-  <si>
     <t>В рамках MVP депозитного направления.</t>
   </si>
   <si>
@@ -139,13 +130,62 @@
   <si>
     <t>В MVP бэк-офис может обрабатывать заявки по старому процессу.
 Желательно такое MVP, чтобы была возможность в будущем при обращении в отделении депозит открывался без участия сотрудников бэк-офиса</t>
+  </si>
+  <si>
+    <t>разработка документации для дальнейшего расширения системы</t>
+  </si>
+  <si>
+    <t>Возможность переключения на резервный ЦОД</t>
+  </si>
+  <si>
+    <t>предусмотреть равномерное горизонтальное масштабирование и распределение запросов между серверами, приложениями и ЦОД</t>
+  </si>
+  <si>
+    <t>Команда АБС утверждает, что база данных системы уже перегружена</t>
+  </si>
+  <si>
+    <t>Считаю, что команда на то и команда, чтобы работать, а не что-то там утверждать и ограничивать архитектуру. Плохо работает? Исправляйте. Меняем архитектуру… А вписываться в текущее нытье, да еще строить на нем будущее - утопия. А то так всегда будет - костыль на костыле сидит и костылем погоняет.</t>
+  </si>
+  <si>
+    <t>ДОБАВЛЕНО</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">В интернет-банке </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="9"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>и сайте</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> клиент видит список доступных депозитов с актуальными ставками и персонализированные ставки лично для него</t>
+    </r>
+  </si>
+  <si>
+    <t>Клиент может подать заявку на депозит на сайте, интернет-банке, оставив свой номер телефона и Ф. И. О.</t>
+  </si>
+  <si>
+    <t>В интернет-банке данные при передаче также надо защитить каким-то механизмом шифрования</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -179,8 +219,15 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -205,6 +252,12 @@
         <bgColor theme="4" tint="-0.249977111117893"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -268,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -306,6 +359,21 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -542,7 +610,11 @@
     <col min="4" max="4" width="44.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="30" customHeight="1"/>
+    <row r="1" spans="2:4" ht="30" customHeight="1">
+      <c r="C1" s="16" t="s">
+        <v>40</v>
+      </c>
+    </row>
     <row r="2" spans="2:4" ht="30" customHeight="1"/>
     <row r="3" spans="2:4" ht="15.75">
       <c r="B3" s="1" t="s">
@@ -564,31 +636,29 @@
       </c>
       <c r="D4" s="13"/>
     </row>
-    <row r="5" spans="2:4" ht="47.25">
+    <row r="5" spans="2:4" ht="63">
       <c r="B5" s="2"/>
-      <c r="C5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>32</v>
-      </c>
+      <c r="C5" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="9"/>
     </row>
     <row r="6" spans="2:4" ht="126">
       <c r="B6" s="2"/>
       <c r="C6" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="78.75">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="94.5">
       <c r="B7" s="5"/>
       <c r="C7" s="10" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="15.75">
@@ -603,7 +673,7 @@
     <row r="9" spans="2:4" ht="63">
       <c r="B9" s="2"/>
       <c r="C9" s="11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D9" s="4"/>
     </row>
@@ -626,16 +696,16 @@
     <row r="12" spans="2:4" ht="78.75">
       <c r="B12" s="2"/>
       <c r="C12" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" ht="15.75">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="31.5">
       <c r="B13" s="5"/>
       <c r="C13" s="3" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="D13" s="4"/>
     </row>
@@ -648,10 +718,10 @@
       </c>
       <c r="D14" s="13"/>
     </row>
-    <row r="15" spans="2:4" ht="15.75">
+    <row r="15" spans="2:4" ht="94.5">
       <c r="B15" s="2"/>
-      <c r="C15" s="6" t="s">
-        <v>5</v>
+      <c r="C15" s="17" t="s">
+        <v>37</v>
       </c>
       <c r="D15" s="4"/>
     </row>
@@ -674,16 +744,16 @@
     <row r="18" spans="1:4" ht="78.75">
       <c r="B18" s="2"/>
       <c r="C18" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15.75">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="47.25">
       <c r="B19" s="5"/>
-      <c r="C19" s="3" t="s">
-        <v>5</v>
+      <c r="C19" s="18" t="s">
+        <v>35</v>
       </c>
       <c r="D19" s="4"/>
     </row>
@@ -703,7 +773,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75">
@@ -713,51 +783,57 @@
         <v>17</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="126">
       <c r="B23" s="5"/>
       <c r="C23" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="63">
       <c r="B24" s="5"/>
       <c r="C24" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D24" s="4"/>
     </row>
     <row r="25" spans="1:4" ht="47.25">
       <c r="B25" s="5"/>
       <c r="C25" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="47.25">
       <c r="B26" s="5"/>
       <c r="C26" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15.75">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="89.25">
       <c r="B27" s="5"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28" spans="1:4" ht="15.75">
+      <c r="C27" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="63">
       <c r="B28" s="5"/>
-      <c r="C28" s="8"/>
+      <c r="C28" s="14" t="s">
+        <v>43</v>
+      </c>
       <c r="D28" s="4"/>
     </row>
   </sheetData>
